--- a/hospital/пол/hospital-floors.xlsx
+++ b/hospital/пол/hospital-floors.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="898"/>
   </bookViews>
   <sheets>
-    <sheet name="1.2пл3в" sheetId="15" r:id="rId1"/>
-    <sheet name="1.3Инв" sheetId="16" r:id="rId2"/>
-    <sheet name="1.1Инв" sheetId="14" r:id="rId3"/>
+    <sheet name="2.1ЛШ" sheetId="17" r:id="rId1"/>
+    <sheet name="1.2пл3в" sheetId="15" r:id="rId2"/>
+    <sheet name="1.3Инв" sheetId="16" r:id="rId3"/>
+    <sheet name="1.1Инв" sheetId="14" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="35">
   <si>
     <t>Ед. изм.</t>
   </si>
@@ -87,6 +88,43 @@
   </si>
   <si>
     <t>Устройство стяжки СКБ / армированная сеткой до 40 мм</t>
+  </si>
+  <si>
+    <t>Засыпка пазух в монолитных конструкциях / песок</t>
+  </si>
+  <si>
+    <t>Песок</t>
+  </si>
+  <si>
+    <t>Армирование ЖБ плиты</t>
+  </si>
+  <si>
+    <t>Бетонирование ЖБ плиты</t>
+  </si>
+  <si>
+    <t>Устройство монолитных плит перекрытий, лестничных площадок нежилых малоэтажных зданий / армированием до 160 кг</t>
+  </si>
+  <si>
+    <t>№
+шахты</t>
+  </si>
+  <si>
+    <t>т</t>
+  </si>
+  <si>
+    <t>Устройство бетонной подготовки</t>
+  </si>
+  <si>
+    <t>Бет. подг.</t>
+  </si>
+  <si>
+    <t>Армир.</t>
+  </si>
+  <si>
+    <t>объем, кг.</t>
+  </si>
+  <si>
+    <t>Бетон</t>
   </si>
 </sst>
 </file>
@@ -213,7 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -248,6 +286,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -275,6 +322,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -284,11 +337,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -595,6 +657,342 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="4">
+        <f>B12</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="32"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4">
+        <f>B18</f>
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>3</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="4">
+        <f>B24</f>
+        <v>292</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="1:10" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>4</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4">
+        <f>B30</f>
+        <v>3.7</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="22"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="1:10" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4">
+        <v>18.5</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4">
+        <v>18.5</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4">
+        <f>SUM(B10:B11)</f>
+        <v>37</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
+        <v>2</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4">
+        <f>SUM(B16:B17)</f>
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>2</v>
+      </c>
+      <c r="B23" s="4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="4">
+        <f>SUM(B22:B23)</f>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
+        <v>2</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2">
+        <f>SUM(B28:B29)</f>
+        <v>3.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="C8:F12"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -608,25 +1006,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
@@ -641,11 +1039,11 @@
       <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
@@ -661,11 +1059,11 @@
       <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
@@ -678,13 +1076,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
@@ -696,10 +1094,10 @@
       <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
@@ -711,10 +1109,10 @@
       <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
@@ -727,10 +1125,10 @@
         <f>B8*0.089</f>
         <v>114.9791</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
@@ -743,10 +1141,10 @@
         <f t="shared" ref="C9:C10" si="0">B9*0.089</f>
         <v>117.22189999999999</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
@@ -759,10 +1157,10 @@
         <f t="shared" si="0"/>
         <v>80.929479999999998</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -776,10 +1174,10 @@
         <f>SUM(C8:C10)</f>
         <v>313.13047999999998</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -794,7 +1192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -812,25 +1210,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
@@ -845,11 +1243,11 @@
       <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="11" t="s">
         <v>19</v>
       </c>
@@ -865,11 +1263,11 @@
       <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="11" t="s">
         <v>20</v>
       </c>
@@ -882,13 +1280,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
@@ -980,7 +1378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -998,25 +1396,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
@@ -1031,11 +1429,11 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1051,11 +1449,11 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1068,13 +1466,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
